--- a/AAII_Financials/Quarterly/GPOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GPOX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>GPOX</t>
   </si>
@@ -656,145 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
-        <v>100</v>
-      </c>
       <c r="G8" s="3">
         <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>600</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -819,49 +823,52 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
         <v>700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="F9" s="3">
-        <v>100</v>
-      </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>200</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
       </c>
       <c r="L9" s="3">
+        <v>200</v>
+      </c>
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -884,49 +891,52 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>-200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1189,8 +1212,8 @@
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
+      <c r="I15" s="3">
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>4</v>
@@ -1207,8 +1230,8 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,49 +1282,50 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
-        <v>100</v>
-      </c>
       <c r="P17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="3">
         <v>0</v>
@@ -1321,50 +1348,53 @@
       <c r="W17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-300</v>
       </c>
       <c r="N18" s="3">
         <v>-300</v>
       </c>
       <c r="O18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
@@ -1386,8 +1416,11 @@
       <c r="W18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1476,55 +1510,58 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-19100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
+      <c r="R21" s="3">
+        <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
@@ -1532,8 +1569,8 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V21" s="3">
         <v>0</v>
@@ -1541,28 +1578,31 @@
       <c r="W21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
-        <v>100</v>
-      </c>
       <c r="G22" s="3">
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1571,10 +1611,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1591,8 +1631,8 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1606,50 +1646,53 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-300</v>
       </c>
       <c r="N23" s="3">
         <v>-300</v>
       </c>
       <c r="O23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
@@ -1671,8 +1714,11 @@
       <c r="W23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,50 +1850,53 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19100</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-300</v>
       </c>
       <c r="N26" s="3">
         <v>-300</v>
       </c>
       <c r="O26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
@@ -1866,50 +1918,53 @@
       <c r="W26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-300</v>
       </c>
       <c r="N27" s="3">
         <v>-300</v>
       </c>
       <c r="O27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
@@ -1931,8 +1986,11 @@
       <c r="W27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2256,50 +2326,53 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19100</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-300</v>
       </c>
       <c r="N33" s="3">
         <v>-300</v>
       </c>
       <c r="O33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
@@ -2321,8 +2394,11 @@
       <c r="W33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,50 +2462,53 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19100</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-300</v>
       </c>
       <c r="N35" s="3">
         <v>-300</v>
       </c>
       <c r="O35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
@@ -2451,78 +2530,84 @@
       <c r="W35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,8 +2657,9 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2583,28 +2670,28 @@
         <v>100</v>
       </c>
       <c r="F41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>200</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -2615,8 +2702,8 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2710,7 +2803,7 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -2725,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2745,8 +2838,8 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
@@ -2766,19 +2859,22 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E44" s="3">
         <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
@@ -2786,8 +2882,8 @@
       <c r="H44" s="3">
         <v>0</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
@@ -2804,8 +2900,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2831,13 +2927,16 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -2846,25 +2945,25 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -2896,46 +2995,49 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>400</v>
+      </c>
+      <c r="E46" s="3">
         <v>500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>600</v>
-      </c>
-      <c r="H46" s="3">
-        <v>400</v>
       </c>
       <c r="I46" s="3">
         <v>400</v>
       </c>
       <c r="J46" s="3">
+        <v>400</v>
+      </c>
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
-        <v>100</v>
-      </c>
       <c r="L46" s="3">
+        <v>100</v>
+      </c>
+      <c r="M46" s="3">
         <v>200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P46" s="3">
         <v>0</v>
@@ -2961,8 +3063,11 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3026,8 +3131,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3035,13 +3143,13 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
-        <v>100</v>
-      </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -3070,8 +3178,8 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
@@ -3091,13 +3199,16 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
@@ -3111,8 +3222,8 @@
       <c r="H49" s="3">
         <v>100</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
+      <c r="I49" s="3">
+        <v>100</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>4</v>
@@ -3129,8 +3240,8 @@
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,8 +3539,11 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3425,43 +3551,43 @@
         <v>800</v>
       </c>
       <c r="E54" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F54" s="3">
         <v>600</v>
       </c>
       <c r="G54" s="3">
+        <v>600</v>
+      </c>
+      <c r="H54" s="3">
         <v>700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>400</v>
-      </c>
-      <c r="I54" s="3">
-        <v>500</v>
       </c>
       <c r="J54" s="3">
         <v>500</v>
       </c>
       <c r="K54" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L54" s="3">
+        <v>100</v>
+      </c>
+      <c r="M54" s="3">
         <v>200</v>
       </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
       <c r="N54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R54" s="3">
         <v>0</v>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,31 +3661,32 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
-      </c>
-      <c r="F57" s="3">
-        <v>400</v>
       </c>
       <c r="G57" s="3">
         <v>400</v>
       </c>
       <c r="H57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -3567,13 +3698,13 @@
         <v>200</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3596,40 +3727,43 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="M58" s="3">
+        <v>100</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
@@ -3646,8 +3780,8 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3661,19 +3795,22 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>200</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
@@ -3685,31 +3822,31 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3600</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
       <c r="N59" s="3">
         <v>0</v>
       </c>
       <c r="O59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S59" s="3">
         <v>100</v>
@@ -3726,55 +3863,58 @@
       <c r="W59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1300</v>
       </c>
       <c r="H60" s="3">
         <v>1300</v>
       </c>
       <c r="I60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
-        <v>100</v>
-      </c>
       <c r="O60" s="3">
+        <v>100</v>
+      </c>
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
-        <v>100</v>
-      </c>
       <c r="Q60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
@@ -3791,8 +3931,11 @@
       <c r="W60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,55 +4271,58 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1300</v>
       </c>
       <c r="H66" s="3">
         <v>1300</v>
       </c>
       <c r="I66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J66" s="3">
         <v>1100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3">
-        <v>100</v>
-      </c>
       <c r="O66" s="3">
+        <v>100</v>
+      </c>
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
-        <v>100</v>
-      </c>
       <c r="Q66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,13 +4501,16 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E70" s="3">
         <v>2000</v>
@@ -4369,13 +4537,13 @@
         <v>2000</v>
       </c>
       <c r="M70" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="N70" s="3">
         <v>200</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,52 +4637,55 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-35700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-34500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-32200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-30800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-23100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-100</v>
       </c>
       <c r="R72" s="3">
         <v>-100</v>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,55 +4909,58 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-4400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-8200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-5600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-100</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
       <c r="Q76" s="3">
         <v>0</v>
       </c>
       <c r="R76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S76" s="3">
         <v>-100</v>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,120 +5045,126 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19100</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-300</v>
       </c>
       <c r="N81" s="3">
         <v>-300</v>
       </c>
       <c r="O81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
         <v>0</v>
       </c>
@@ -4991,8 +5186,11 @@
       <c r="W81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5048,8 +5247,8 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
@@ -5066,8 +5265,8 @@
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,40 +5620,43 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-300</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="I89" s="3">
         <v>-100</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>-200</v>
       </c>
       <c r="M89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
@@ -5448,7 +5665,7 @@
         <v>-100</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5531,17 +5752,17 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,8 +5918,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5726,14 +5956,14 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -5741,14 +5971,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,52 +6284,55 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>400</v>
       </c>
       <c r="F100" s="3">
         <v>400</v>
       </c>
       <c r="G100" s="3">
+        <v>400</v>
+      </c>
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
-        <v>100</v>
-      </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>100</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -6106,8 +6352,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,8 +6420,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6180,31 +6432,31 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -6234,6 +6486,9 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GPOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GPOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>GPOX</t>
   </si>
@@ -656,152 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
-        <v>100</v>
-      </c>
       <c r="H8" s="3">
         <v>100</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -826,52 +830,55 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
-        <v>100</v>
-      </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>200</v>
       </c>
       <c r="L9" s="3">
         <v>200</v>
       </c>
       <c r="M9" s="3">
+        <v>200</v>
+      </c>
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
@@ -894,8 +901,11 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -903,43 +913,43 @@
         <v>200</v>
       </c>
       <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>-200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1215,8 +1238,8 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>4</v>
@@ -1233,8 +1256,8 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,52 +1309,53 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
-        <v>100</v>
-      </c>
       <c r="Q17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17" s="3">
         <v>0</v>
@@ -1351,53 +1378,56 @@
       <c r="X17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-300</v>
       </c>
       <c r="O18" s="3">
         <v>-300</v>
       </c>
       <c r="P18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
@@ -1419,8 +1449,11 @@
       <c r="X18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1513,8 +1547,11 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1522,49 +1559,49 @@
         <v>-700</v>
       </c>
       <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R21" s="3">
         <v>0</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
+      <c r="S21" s="3">
+        <v>0</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
@@ -1572,8 +1609,8 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
+      <c r="V21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
@@ -1581,31 +1618,34 @@
       <c r="X21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1614,10 +1654,10 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
@@ -1634,8 +1674,8 @@
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1649,53 +1689,56 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-300</v>
       </c>
       <c r="O23" s="3">
         <v>-300</v>
       </c>
       <c r="P23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
@@ -1717,8 +1760,11 @@
       <c r="X23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,53 +1902,56 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-300</v>
       </c>
       <c r="O26" s="3">
         <v>-300</v>
       </c>
       <c r="P26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
@@ -1921,53 +1973,56 @@
       <c r="X26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-300</v>
       </c>
       <c r="O27" s="3">
         <v>-300</v>
       </c>
       <c r="P27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
@@ -1989,8 +2044,11 @@
       <c r="X27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2329,53 +2399,56 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-300</v>
       </c>
       <c r="O33" s="3">
         <v>-300</v>
       </c>
       <c r="P33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
@@ -2397,8 +2470,11 @@
       <c r="X33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,53 +2541,56 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-300</v>
       </c>
       <c r="O35" s="3">
         <v>-300</v>
       </c>
       <c r="P35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
@@ -2533,81 +2612,87 @@
       <c r="X35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,13 +2744,14 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
@@ -2673,28 +2760,28 @@
         <v>100</v>
       </c>
       <c r="G41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3">
         <v>200</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
@@ -2705,8 +2792,8 @@
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,19 +2884,22 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -2821,13 +2914,13 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2841,8 +2934,8 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
@@ -2862,22 +2955,25 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>400</v>
+      </c>
+      <c r="E44" s="3">
         <v>300</v>
-      </c>
-      <c r="E44" s="3">
-        <v>200</v>
       </c>
       <c r="F44" s="3">
         <v>200</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -2885,8 +2981,8 @@
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
+      <c r="J44" s="3">
+        <v>0</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
@@ -2903,8 +2999,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2939,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -2948,25 +3047,25 @@
         <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
@@ -2998,49 +3097,52 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>900</v>
+      </c>
+      <c r="E46" s="3">
         <v>400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>600</v>
-      </c>
-      <c r="I46" s="3">
-        <v>400</v>
       </c>
       <c r="J46" s="3">
         <v>400</v>
       </c>
       <c r="K46" s="3">
+        <v>400</v>
+      </c>
+      <c r="L46" s="3">
         <v>500</v>
       </c>
-      <c r="L46" s="3">
-        <v>100</v>
-      </c>
       <c r="M46" s="3">
+        <v>100</v>
+      </c>
+      <c r="N46" s="3">
         <v>200</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
       <c r="O46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,8 +3239,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3146,13 +3254,13 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
+        <v>300</v>
+      </c>
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
-        <v>100</v>
-      </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>0</v>
@@ -3181,8 +3289,8 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
@@ -3202,8 +3310,11 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3211,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>100</v>
@@ -3225,8 +3336,8 @@
       <c r="I49" s="3">
         <v>100</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="J49" s="3">
+        <v>100</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -3243,8 +3354,8 @@
       <c r="O49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3523,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,55 +3665,58 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E54" s="3">
         <v>800</v>
       </c>
       <c r="F54" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="G54" s="3">
         <v>600</v>
       </c>
       <c r="H54" s="3">
+        <v>600</v>
+      </c>
+      <c r="I54" s="3">
         <v>700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>400</v>
-      </c>
-      <c r="J54" s="3">
-        <v>500</v>
       </c>
       <c r="K54" s="3">
         <v>500</v>
       </c>
       <c r="L54" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="M54" s="3">
+        <v>100</v>
+      </c>
+      <c r="N54" s="3">
         <v>200</v>
       </c>
-      <c r="N54" s="3">
-        <v>0</v>
-      </c>
       <c r="O54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S54" s="3">
         <v>0</v>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,34 +3792,35 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>400</v>
       </c>
       <c r="H57" s="3">
         <v>400</v>
       </c>
       <c r="I57" s="3">
+        <v>400</v>
+      </c>
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -3701,13 +3832,13 @@
         <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3730,43 +3861,46 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="E58" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="F58" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>300</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="N58" s="3">
+        <v>100</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
@@ -3783,8 +3917,8 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3798,22 +3932,25 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>200</v>
@@ -3825,31 +3962,31 @@
         <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>200</v>
+      </c>
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3600</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
       <c r="P59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T59" s="3">
         <v>100</v>
@@ -3866,58 +4003,61 @@
       <c r="X59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3900</v>
+        <v>4900</v>
       </c>
       <c r="E60" s="3">
-        <v>3200</v>
+        <v>3700</v>
       </c>
       <c r="F60" s="3">
-        <v>2500</v>
+        <v>3100</v>
       </c>
       <c r="G60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H60" s="3">
         <v>1600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1300</v>
       </c>
       <c r="I60" s="3">
         <v>1300</v>
       </c>
       <c r="J60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
-        <v>100</v>
-      </c>
       <c r="P60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>100</v>
-      </c>
       <c r="R60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
@@ -3934,22 +4074,25 @@
       <c r="X60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,58 +4429,61 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1300</v>
       </c>
       <c r="I66" s="3">
         <v>1300</v>
       </c>
       <c r="J66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3">
-        <v>100</v>
-      </c>
       <c r="P66" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3">
-        <v>100</v>
-      </c>
       <c r="R66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4513,7 +4681,7 @@
         <v>1900</v>
       </c>
       <c r="E70" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="F70" s="3">
         <v>2000</v>
@@ -4540,13 +4708,13 @@
         <v>2000</v>
       </c>
       <c r="N70" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="O70" s="3">
         <v>200</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,55 +4811,58 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-36700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-35700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-34500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-30500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-23100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-100</v>
       </c>
       <c r="S72" s="3">
         <v>-100</v>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,58 +5095,61 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-5000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-8200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-5600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-100</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
       <c r="R76" s="3">
         <v>0</v>
       </c>
       <c r="S76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T76" s="3">
         <v>-100</v>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,126 +5237,132 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-300</v>
       </c>
       <c r="O81" s="3">
         <v>-300</v>
       </c>
       <c r="P81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
@@ -5189,8 +5384,11 @@
       <c r="X81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5250,8 +5449,8 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -5268,8 +5467,8 @@
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,43 +5837,46 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-300</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
       </c>
       <c r="I89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="J89" s="3">
         <v>-100</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M89" s="3">
         <v>-200</v>
       </c>
       <c r="N89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="O89" s="3">
         <v>-100</v>
@@ -5668,7 +5885,7 @@
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5755,17 +5976,17 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6148,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5959,14 +6189,14 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -5974,14 +6204,14 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,55 +6530,58 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
-      </c>
-      <c r="F100" s="3">
-        <v>400</v>
       </c>
       <c r="G100" s="3">
         <v>400</v>
       </c>
       <c r="H100" s="3">
+        <v>400</v>
+      </c>
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
-        <v>100</v>
-      </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>100</v>
+      </c>
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
-        <v>100</v>
-      </c>
       <c r="O100" s="3">
+        <v>100</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,43 +6672,46 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -6489,6 +6741,9 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GPOX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GPOX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>GPOX</t>
   </si>
@@ -656,114 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,44 +774,44 @@
         <v>1100</v>
       </c>
       <c r="E8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
-        <v>100</v>
-      </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>600</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -833,55 +836,58 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>800</v>
+      </c>
+      <c r="E9" s="3">
         <v>900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3">
-        <v>100</v>
-      </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>200</v>
       </c>
       <c r="M9" s="3">
         <v>200</v>
       </c>
       <c r="N9" s="3">
+        <v>200</v>
+      </c>
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
+      <c r="R9" s="3">
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
@@ -904,55 +910,58 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>-200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
@@ -975,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1160,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,8 +1234,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1241,8 +1263,8 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>4</v>
@@ -1259,8 +1281,8 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,55 +1335,56 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
-        <v>100</v>
-      </c>
       <c r="R17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17" s="3">
         <v>0</v>
@@ -1381,56 +1407,59 @@
       <c r="Y17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-300</v>
       </c>
       <c r="P18" s="3">
         <v>-300</v>
       </c>
       <c r="Q18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
@@ -1452,8 +1481,11 @@
       <c r="Y18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1550,61 +1583,64 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-700</v>
+        <v>-1500</v>
       </c>
       <c r="E21" s="3">
         <v>-700</v>
       </c>
       <c r="F21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S21" s="3">
         <v>0</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
+      <c r="T21" s="3">
+        <v>0</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
@@ -1612,8 +1648,8 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
+      <c r="W21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X21" s="3">
         <v>0</v>
@@ -1621,34 +1657,37 @@
       <c r="Y21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
-        <v>100</v>
-      </c>
       <c r="I22" s="3">
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1657,10 +1696,10 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
@@ -1677,8 +1716,8 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1692,56 +1731,59 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-300</v>
       </c>
       <c r="P23" s="3">
         <v>-300</v>
       </c>
       <c r="Q23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
@@ -1763,8 +1805,11 @@
       <c r="Y23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1834,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,56 +1953,59 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-300</v>
       </c>
       <c r="P26" s="3">
         <v>-300</v>
       </c>
       <c r="Q26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
@@ -1976,56 +2027,59 @@
       <c r="Y26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19100</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-300</v>
       </c>
       <c r="P27" s="3">
         <v>-300</v>
       </c>
       <c r="Q27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
@@ -2047,8 +2101,11 @@
       <c r="Y27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2402,56 +2471,59 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-300</v>
       </c>
       <c r="P33" s="3">
         <v>-300</v>
       </c>
       <c r="Q33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
@@ -2473,8 +2545,11 @@
       <c r="Y33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,56 +2619,59 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-300</v>
       </c>
       <c r="P35" s="3">
         <v>-300</v>
       </c>
       <c r="Q35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
@@ -2615,84 +2693,90 @@
       <c r="Y35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,17 +2830,18 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
-        <v>100</v>
-      </c>
       <c r="F41" s="3">
         <v>100</v>
       </c>
@@ -2763,28 +2849,28 @@
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3">
         <v>200</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41" s="3">
         <v>0</v>
@@ -2795,8 +2881,8 @@
       <c r="R41" s="3">
         <v>0</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
@@ -2816,8 +2902,11 @@
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,22 +2976,25 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -2917,13 +3009,13 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2937,8 +3029,8 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
@@ -2958,8 +3050,11 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2967,16 +3062,16 @@
         <v>400</v>
       </c>
       <c r="E44" s="3">
+        <v>400</v>
+      </c>
+      <c r="F44" s="3">
         <v>300</v>
-      </c>
-      <c r="F44" s="3">
-        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>200</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I44" s="3">
         <v>0</v>
@@ -2984,8 +3079,8 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
@@ -3002,8 +3097,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3029,8 +3124,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3041,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -3050,25 +3148,25 @@
         <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -3100,52 +3198,55 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>600</v>
+      </c>
+      <c r="E46" s="3">
         <v>900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>600</v>
-      </c>
-      <c r="J46" s="3">
-        <v>400</v>
       </c>
       <c r="K46" s="3">
         <v>400</v>
       </c>
       <c r="L46" s="3">
+        <v>400</v>
+      </c>
+      <c r="M46" s="3">
         <v>500</v>
       </c>
-      <c r="M46" s="3">
-        <v>100</v>
-      </c>
       <c r="N46" s="3">
+        <v>100</v>
+      </c>
+      <c r="O46" s="3">
         <v>200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
@@ -3171,8 +3272,11 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,8 +3346,11 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3257,13 +3364,13 @@
         <v>300</v>
       </c>
       <c r="G48" s="3">
+        <v>300</v>
+      </c>
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
-        <v>100</v>
-      </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3292,8 +3399,8 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
@@ -3313,8 +3420,11 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3325,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>100</v>
@@ -3339,8 +3449,8 @@
       <c r="J49" s="3">
         <v>100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>100</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
@@ -3357,8 +3467,8 @@
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,58 +3790,61 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1200</v>
-      </c>
-      <c r="E54" s="3">
-        <v>800</v>
       </c>
       <c r="F54" s="3">
         <v>800</v>
       </c>
       <c r="G54" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="H54" s="3">
         <v>600</v>
       </c>
       <c r="I54" s="3">
+        <v>600</v>
+      </c>
+      <c r="J54" s="3">
         <v>700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>400</v>
-      </c>
-      <c r="K54" s="3">
-        <v>500</v>
       </c>
       <c r="L54" s="3">
         <v>500</v>
       </c>
       <c r="M54" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="N54" s="3">
+        <v>100</v>
+      </c>
+      <c r="O54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
       <c r="P54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T54" s="3">
         <v>0</v>
@@ -3739,8 +3864,11 @@
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,37 +3922,38 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>400</v>
       </c>
       <c r="I57" s="3">
         <v>400</v>
       </c>
       <c r="J57" s="3">
+        <v>400</v>
+      </c>
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -3835,13 +3965,13 @@
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3864,46 +3994,49 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>300</v>
       </c>
       <c r="M58" s="3">
         <v>300</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="O58" s="3">
+        <v>100</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
@@ -3920,8 +4053,8 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3935,25 +4068,28 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
@@ -3965,31 +4101,31 @@
         <v>200</v>
       </c>
       <c r="L59" s="3">
+        <v>200</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
       <c r="Q59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
@@ -4006,61 +4142,64 @@
       <c r="Y59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
         <v>4900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1300</v>
       </c>
       <c r="J60" s="3">
         <v>1300</v>
       </c>
       <c r="K60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
-        <v>100</v>
-      </c>
       <c r="Q60" s="3">
+        <v>100</v>
+      </c>
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
-        <v>100</v>
-      </c>
       <c r="S60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
@@ -4077,25 +4216,28 @@
       <c r="Y60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -4148,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,61 +4586,64 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1300</v>
       </c>
       <c r="J66" s="3">
         <v>1300</v>
       </c>
       <c r="K66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
-        <v>100</v>
-      </c>
       <c r="Q66" s="3">
+        <v>100</v>
+      </c>
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3">
-        <v>100</v>
-      </c>
       <c r="S66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U66" s="3">
         <v>100</v>
@@ -4503,8 +4660,11 @@
       <c r="Y66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4684,7 +4851,7 @@
         <v>1900</v>
       </c>
       <c r="F70" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G70" s="3">
         <v>2000</v>
@@ -4711,13 +4878,13 @@
         <v>2000</v>
       </c>
       <c r="O70" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="P70" s="3">
         <v>200</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,58 +4984,61 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-37600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-36700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-35700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-33100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-32200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-30800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-30500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-29900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-100</v>
       </c>
       <c r="T72" s="3">
         <v>-100</v>
@@ -4885,8 +5058,11 @@
       <c r="Y72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,61 +5280,64 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-5700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-5000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-3100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-2700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-3000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-8200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-5600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-100</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
       <c r="T76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U76" s="3">
         <v>-100</v>
@@ -5169,8 +5354,11 @@
       <c r="Y76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,132 +5428,138 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-300</v>
       </c>
       <c r="P81" s="3">
         <v>-300</v>
       </c>
       <c r="Q81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
@@ -5387,8 +5581,11 @@
       <c r="Y81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5452,8 +5650,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -5470,8 +5668,8 @@
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,46 +6053,49 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-300</v>
       </c>
       <c r="I89" s="3">
         <v>-300</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="K89" s="3">
         <v>-100</v>
       </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
         <v>-200</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
@@ -5888,7 +6104,7 @@
         <v>-100</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -5911,8 +6127,11 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5979,17 +6199,17 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -6009,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,8 +6377,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6192,14 +6421,14 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -6207,14 +6436,14 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6222,8 +6451,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,58 +6775,61 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>400</v>
       </c>
       <c r="H100" s="3">
         <v>400</v>
       </c>
       <c r="I100" s="3">
+        <v>400</v>
+      </c>
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
-        <v>100</v>
-      </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
-        <v>100</v>
-      </c>
       <c r="P100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -6604,8 +6849,11 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,46 +6923,49 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
@@ -6744,6 +6995,9 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>
